--- a/docs/Mapping_casi_uso/matrimoni/Matr_002.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_002.xlsx
@@ -869,7 +869,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -878,7 +878,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -887,7 +887,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposo</t>
@@ -914,7 +914,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposa</t>
@@ -935,13 +935,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -950,7 +950,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -959,13 +959,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -974,7 +974,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Interprete</t>
@@ -1091,13 +1091,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1201,7 +1201,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10662,10 +10662,10 @@
         <v>283</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>284</v>
@@ -11306,10 +11306,10 @@
         <v>286</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>287</v>
@@ -11950,10 +11950,10 @@
         <v>289</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D468" s="2" t="s">
         <v>290</v>
@@ -12778,10 +12778,10 @@
         <v>298</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D504" s="2" t="s">
         <v>299</v>
@@ -13606,10 +13606,10 @@
         <v>305</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>306</v>
@@ -14250,10 +14250,10 @@
         <v>308</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D568" s="2" t="s">
         <v>306</v>
@@ -15055,10 +15055,10 @@
         <v>313</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>314</v>
@@ -15699,10 +15699,10 @@
         <v>316</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>314</v>
@@ -16907,7 +16907,7 @@
         <v>360</v>
       </c>
       <c r="F683" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G683" s="2" t="s">
         <v>60</v>
